--- a/data/trans_dic/P19F$tarde-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19F$tarde-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la tarde</t>
+          <t>Población que, al menos, se cepilla los dientes por la tarde (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,76; 30,48</t>
+          <t>16,64; 30,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,49; 34,66</t>
+          <t>20,71; 35,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,35; 30,36</t>
+          <t>20,51; 29,93</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,64; 39,81</t>
+          <t>27,06; 39,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,27; 37,14</t>
+          <t>25,55; 38,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,0; 36,81</t>
+          <t>28,27; 37,01</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,11; 44,78</t>
+          <t>28,76; 44,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,29; 30,73</t>
+          <t>13,75; 30,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,84; 36,46</t>
+          <t>24,12; 35,38</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,11; 31,85</t>
+          <t>19,18; 31,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,38; 29,13</t>
+          <t>17,71; 29,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,88; 28,31</t>
+          <t>19,66; 28,22</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,0; 56,97</t>
+          <t>41,93; 57,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,75; 60,26</t>
+          <t>44,11; 59,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,19; 56,2</t>
+          <t>44,73; 56,29</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,3; 44,32</t>
+          <t>29,14; 44,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39,28; 53,88</t>
+          <t>38,73; 53,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,94; 47,33</t>
+          <t>35,9; 47,67</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,34; 32,03</t>
+          <t>22,45; 32,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,9; 36,98</t>
+          <t>26,84; 36,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,3; 32,83</t>
+          <t>25,83; 32,64</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,36; 33,03</t>
+          <t>23,46; 33,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,29; 33,81</t>
+          <t>23,59; 33,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,56; 31,28</t>
+          <t>24,44; 31,86</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,74; 32,97</t>
+          <t>28,56; 33,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29,8; 34,25</t>
+          <t>29,96; 34,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29,6; 32,88</t>
+          <t>29,71; 32,95</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la tarde</t>
+          <t>Población que, al menos, se cepilla los dientes por la tarde (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>30045; 54632</t>
+          <t>29819; 54774</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33174; 56113</t>
+          <t>33518; 56758</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69431; 103562</t>
+          <t>69957; 102115</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70016; 100844</t>
+          <t>68554; 100492</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59872; 87974</t>
+          <t>60520; 90334</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>137258; 180466</t>
+          <t>138576; 181436</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>40085; 61651</t>
+          <t>39600; 61353</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13952; 30003</t>
+          <t>13423; 29306</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58453; 85797</t>
+          <t>56761; 83254</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39933; 66556</t>
+          <t>40068; 66132</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39316; 65911</t>
+          <t>40059; 66810</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86518; 123197</t>
+          <t>85555; 122804</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>59653; 82887</t>
+          <t>61005; 83366</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>64702; 89107</t>
+          <t>65226; 87505</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>132568; 164872</t>
+          <t>131226; 165136</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41637; 65196</t>
+          <t>42876; 66154</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>69897; 95881</t>
+          <t>68925; 95843</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>116844; 153866</t>
+          <t>116691; 154948</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>85150; 122088</t>
+          <t>85567; 122008</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>96907; 133209</t>
+          <t>96677; 132871</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>194952; 243403</t>
+          <t>191471; 241974</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>76104; 107620</t>
+          <t>76433; 109471</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>77734; 112871</t>
+          <t>78761; 111999</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>162041; 206367</t>
+          <t>161191; 210136</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>511174; 586444</t>
+          <t>508029; 588603</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>519259; 596831</t>
+          <t>522131; 603307</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1042418; 1157740</t>
+          <t>1046212; 1160166</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19F$tarde-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19F$tarde-Provincia-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,64; 30,56</t>
+          <t>16,21; 30,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,71; 35,06</t>
+          <t>21,0; 34,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,51; 29,93</t>
+          <t>20,24; 30,05</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,06; 39,67</t>
+          <t>27,68; 39,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,55; 38,13</t>
+          <t>25,88; 38,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,27; 37,01</t>
+          <t>28,58; 36,9</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,76; 44,56</t>
+          <t>29,17; 45,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,75; 30,02</t>
+          <t>13,61; 30,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,12; 35,38</t>
+          <t>24,07; 35,91</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,18; 31,65</t>
+          <t>19,22; 31,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,71; 29,53</t>
+          <t>17,56; 29,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,66; 28,22</t>
+          <t>20,09; 28,57</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,93; 57,3</t>
+          <t>40,97; 57,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44,11; 59,17</t>
+          <t>44,0; 60,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44,73; 56,29</t>
+          <t>45,18; 56,48</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29,14; 44,97</t>
+          <t>28,9; 44,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38,73; 53,86</t>
+          <t>38,67; 53,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,9; 47,67</t>
+          <t>36,56; 48,01</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,45; 32,01</t>
+          <t>22,89; 32,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,84; 36,88</t>
+          <t>26,95; 36,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25,83; 32,64</t>
+          <t>26,16; 33,41</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,46; 33,6</t>
+          <t>22,74; 33,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,59; 33,55</t>
+          <t>23,5; 33,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,44; 31,86</t>
+          <t>24,39; 31,36</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,56; 33,09</t>
+          <t>28,43; 33,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29,96; 34,62</t>
+          <t>29,82; 34,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29,71; 32,95</t>
+          <t>29,95; 33,01</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29819; 54774</t>
+          <t>29048; 54092</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33518; 56758</t>
+          <t>33995; 56590</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69957; 102115</t>
+          <t>69051; 102518</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68554; 100492</t>
+          <t>70122; 99801</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60520; 90334</t>
+          <t>61303; 90559</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>138576; 181436</t>
+          <t>140109; 180894</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39600; 61353</t>
+          <t>40156; 62438</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13423; 29306</t>
+          <t>13283; 29894</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56761; 83254</t>
+          <t>56650; 84492</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40068; 66132</t>
+          <t>40168; 65356</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40059; 66810</t>
+          <t>39728; 66133</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85555; 122804</t>
+          <t>87413; 124316</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>61005; 83366</t>
+          <t>59606; 83308</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>65226; 87505</t>
+          <t>65064; 88790</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>131226; 165136</t>
+          <t>132536; 165702</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>42876; 66154</t>
+          <t>42511; 65533</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>68925; 95843</t>
+          <t>68809; 95799</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>116691; 154948</t>
+          <t>118856; 156071</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>85567; 122008</t>
+          <t>87263; 124255</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>96677; 132871</t>
+          <t>97094; 132753</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>191471; 241974</t>
+          <t>193944; 247694</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>76433; 109471</t>
+          <t>74104; 107688</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>78761; 111999</t>
+          <t>78445; 111555</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>161191; 210136</t>
+          <t>160867; 206901</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>508029; 588603</t>
+          <t>505745; 589137</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>522131; 603307</t>
+          <t>519547; 596318</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1046212; 1160166</t>
+          <t>1054609; 1162218</t>
         </is>
       </c>
     </row>
